--- a/proposal/chuangzhihui-30-events-table-v3.xlsx
+++ b/proposal/chuangzhihui-30-events-table-v3.xlsx
@@ -460,7 +460,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
@@ -2728,7 +2728,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
@@ -2878,7 +2878,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
